--- a/content/test/data/event-schedule.xlsx
+++ b/content/test/data/event-schedule.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="52">
   <si>
     <t>Date</t>
   </si>
@@ -143,6 +143,30 @@
   </si>
   <si>
     <t>Test Event — em dash time separator</t>
+  </si>
+  <si>
+    <t>2/8/2026</t>
+  </si>
+  <si>
+    <t>7:00 PM - 8:00 PM</t>
+  </si>
+  <si>
+    <t>Test Event — a deliberately long description meant to exercise text wrapping on the Schedule page: an evening of advanced choreography, several guest callers, and a community reception immediately following the main program</t>
+  </si>
+  <si>
+    <t>2/9/2026</t>
+  </si>
+  <si>
+    <t>Test Event</t>
+  </si>
+  <si>
+    <t>2/10/2026</t>
+  </si>
+  <si>
+    <t>Café Montréal Hall</t>
+  </si>
+  <si>
+    <t>Test Event — Soirée Dansante</t>
   </si>
 </sst>
 </file>
@@ -519,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -704,8 +728,50 @@
         <v>43</v>
       </c>
     </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>